--- a/backend/data/financials_by_company/002010.SZ.xlsx
+++ b/backend/data/financials_by_company/002010.SZ.xlsx
@@ -692,658 +692,658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-142561052.3125</v>
+        <v>-7519636.146293</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.218592</v>
       </c>
       <c r="D2" t="n">
-        <v>2037655854.3</v>
+        <v>3909379913.89</v>
       </c>
       <c r="E2" t="n">
-        <v>-570244209.25</v>
+        <v>-34400372.68</v>
       </c>
       <c r="F2" t="n">
-        <v>-570244209.25</v>
+        <v>-34400372.68</v>
       </c>
       <c r="G2" t="n">
-        <v>151656618.41</v>
+        <v>2249436914.27</v>
       </c>
       <c r="H2" t="n">
-        <v>425035710.14</v>
+        <v>429820434.44</v>
       </c>
       <c r="I2" t="n">
-        <v>23121299454.14</v>
+        <v>31897889901.82</v>
       </c>
       <c r="J2" t="n">
-        <v>1467411645.05</v>
+        <v>3874979541.21</v>
       </c>
       <c r="K2" t="n">
-        <v>1042375934.91</v>
+        <v>3445159106.77</v>
       </c>
       <c r="L2" t="n">
-        <v>-459255239.66</v>
+        <v>-461534085.77</v>
       </c>
       <c r="M2" t="n">
-        <v>554855426.47</v>
+        <v>524516148.83</v>
       </c>
       <c r="N2" t="n">
-        <v>103137736.14</v>
+        <v>82925996.81999999</v>
       </c>
       <c r="O2" t="n">
-        <v>579339775.3475</v>
+        <v>2276317650.803707</v>
       </c>
       <c r="P2" t="n">
-        <v>151656618.41</v>
+        <v>2249436914.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>25381547485.98</v>
+        <v>32355817866.23</v>
       </c>
       <c r="R2" t="n">
-        <v>29246208.44</v>
+        <v>35629987.35</v>
       </c>
       <c r="S2" t="n">
-        <v>655231558.11</v>
+        <v>2929282726.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2765466719</v>
+        <v>3168221006</v>
       </c>
       <c r="U2" t="n">
-        <v>2765466719</v>
+        <v>3124217936</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0558</v>
+        <v>0.71</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0558</v>
+        <v>0.72</v>
       </c>
       <c r="X2" t="n">
-        <v>151656618.41</v>
+        <v>2249436914.27</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>151656618.41</v>
+        <v>2249436914.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>-133808515.7</v>
+        <v>-32777717.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>285465134.11</v>
+        <v>2282214631.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>285465134.11</v>
+        <v>2282214631.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>202055374.33</v>
+        <v>638428326.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>487520508.44</v>
+        <v>2920642957.94</v>
       </c>
       <c r="AF2" t="n">
-        <v>-167711049.67</v>
+        <v>-8639768.810000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>-463228533.57</v>
+        <v>-111679124.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>103059331.33</v>
+        <v>14316173.74</v>
       </c>
       <c r="AI2" t="n">
-        <v>243044068.62</v>
+        <v>71216245.94</v>
       </c>
       <c r="AJ2" t="n">
-        <v>117125133.62</v>
+        <v>26146704.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>-459255239.66</v>
+        <v>-461534085.77</v>
       </c>
       <c r="AL2" t="n">
-        <v>7537549.33</v>
+        <v>19943933.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>554855426.47</v>
+        <v>524516148.83</v>
       </c>
       <c r="AN2" t="n">
-        <v>103137736.14</v>
+        <v>82925996.81999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>1335809885.06</v>
+        <v>3155939994.54</v>
       </c>
       <c r="AP2" t="n">
-        <v>2260248031.84</v>
+        <v>457927964.41</v>
       </c>
       <c r="AQ2" t="n">
-        <v>346534437.18</v>
+        <v>341604497.39</v>
       </c>
       <c r="AR2" t="n">
-        <v>140551194.89</v>
+        <v>121416720.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>140551194.89</v>
+        <v>121416720.58</v>
       </c>
       <c r="AT2" t="n">
-        <v>452867236.91</v>
+        <v>429427927.47</v>
       </c>
       <c r="AU2" t="n">
-        <v>488553568.22</v>
+        <v>530849031.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>220535677.5</v>
+        <v>187942451.41</v>
       </c>
       <c r="AW2" t="n">
-        <v>268017890.72</v>
+        <v>342906579.69</v>
       </c>
       <c r="AX2" t="n">
-        <v>29246208.44</v>
+        <v>35629987.35</v>
       </c>
       <c r="AY2" t="n">
-        <v>3596057916.9</v>
+        <v>3613867958.95</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23121299454.14</v>
+        <v>31897889901.82</v>
       </c>
       <c r="BA2" t="n">
-        <v>26717357371.04</v>
+        <v>35511757860.77</v>
       </c>
       <c r="BB2" t="n">
-        <v>26717357371.04</v>
+        <v>35511757860.77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-46424365.385731</v>
+        <v>-72084719.51682</v>
       </c>
       <c r="C3" t="n">
-        <v>0.263797</v>
+        <v>0.290015</v>
       </c>
       <c r="D3" t="n">
-        <v>2164152550.11</v>
+        <v>2323373301.63</v>
       </c>
       <c r="E3" t="n">
-        <v>-175985303.78</v>
+        <v>-248555147.76</v>
       </c>
       <c r="F3" t="n">
-        <v>-175985303.78</v>
+        <v>-248555147.76</v>
       </c>
       <c r="G3" t="n">
-        <v>590940784.1900001</v>
+        <v>745156340.26</v>
       </c>
       <c r="H3" t="n">
-        <v>445207869.09</v>
+        <v>386065988.02</v>
       </c>
       <c r="I3" t="n">
-        <v>30033337008.79</v>
+        <v>33590852046.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1988167246.33</v>
+        <v>2074818153.87</v>
       </c>
       <c r="K3" t="n">
-        <v>1542959377.24</v>
+        <v>1688752165.85</v>
       </c>
       <c r="L3" t="n">
-        <v>-492590215.89</v>
+        <v>-476517412.05</v>
       </c>
       <c r="M3" t="n">
-        <v>596924173.01</v>
+        <v>541198550.7</v>
       </c>
       <c r="N3" t="n">
-        <v>111515808.53</v>
+        <v>72869315.59</v>
       </c>
       <c r="O3" t="n">
-        <v>720501722.584269</v>
+        <v>921626768.50318</v>
       </c>
       <c r="P3" t="n">
-        <v>590940784.1900001</v>
+        <v>745156340.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>32224000337.64</v>
+        <v>35533432224.66</v>
       </c>
       <c r="R3" t="n">
-        <v>27095543.93</v>
+        <v>32052783.04</v>
       </c>
       <c r="S3" t="n">
-        <v>973528606.37</v>
+        <v>1160728425.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2814003734</v>
+        <v>2865985924</v>
       </c>
       <c r="U3" t="n">
-        <v>2814003734</v>
+        <v>2865985924</v>
       </c>
       <c r="V3" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="W3" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="X3" t="n">
-        <v>590940784.1900001</v>
+        <v>745156340.26</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>590940784.1900001</v>
+        <v>745156340.26</v>
       </c>
       <c r="AA3" t="n">
-        <v>-105533331.44</v>
+        <v>-69589520.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>696474115.63</v>
+        <v>814745861.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>696474115.63</v>
+        <v>814745861.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>249561088.6</v>
+        <v>332807754.03</v>
       </c>
       <c r="AE3" t="n">
-        <v>946035204.23</v>
+        <v>1147553615.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>-27493402.14</v>
+        <v>-13120300.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>-202182179.71</v>
+        <v>-208465887.51</v>
       </c>
       <c r="AH3" t="n">
-        <v>-46738031.5</v>
+        <v>3337225.55</v>
       </c>
       <c r="AI3" t="n">
-        <v>173776795.55</v>
+        <v>183471119.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75143415.66</v>
+        <v>21657542.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>-492590215.89</v>
+        <v>-476517412.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>7181851.41</v>
+        <v>8188176.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>596924173.01</v>
+        <v>541198550.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>111515808.53</v>
+        <v>72869315.59</v>
       </c>
       <c r="AO3" t="n">
-        <v>1413318376.79</v>
+        <v>1464285484.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2190663328.85</v>
+        <v>1942580178.51</v>
       </c>
       <c r="AQ3" t="n">
-        <v>407129950.94</v>
+        <v>373589379.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>124265926.33</v>
+        <v>116317120.91</v>
       </c>
       <c r="AS3" t="n">
-        <v>124265926.33</v>
+        <v>116317120.91</v>
       </c>
       <c r="AT3" t="n">
-        <v>401450405.76</v>
+        <v>380695635.11</v>
       </c>
       <c r="AU3" t="n">
-        <v>456812799.19</v>
+        <v>441765514.62</v>
       </c>
       <c r="AV3" t="n">
-        <v>221282000.75</v>
+        <v>198749393.02</v>
       </c>
       <c r="AW3" t="n">
-        <v>235530798.44</v>
+        <v>243016121.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>27095543.93</v>
+        <v>32052783.04</v>
       </c>
       <c r="AY3" t="n">
-        <v>3603981705.64</v>
+        <v>3406865662.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>30033337008.79</v>
+        <v>33590852046.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>33637318714.43</v>
+        <v>36997717708.76</v>
       </c>
       <c r="BB3" t="n">
-        <v>33637318714.43</v>
+        <v>36997717708.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-72084719.51682</v>
+        <v>-46424365.385731</v>
       </c>
       <c r="C4" t="n">
-        <v>0.290015</v>
+        <v>0.263797</v>
       </c>
       <c r="D4" t="n">
-        <v>2323373301.63</v>
+        <v>2164152550.11</v>
       </c>
       <c r="E4" t="n">
-        <v>-248555147.76</v>
+        <v>-175985303.78</v>
       </c>
       <c r="F4" t="n">
-        <v>-248555147.76</v>
+        <v>-175985303.78</v>
       </c>
       <c r="G4" t="n">
-        <v>745156340.26</v>
+        <v>590940784.1900001</v>
       </c>
       <c r="H4" t="n">
-        <v>386065988.02</v>
+        <v>445207869.09</v>
       </c>
       <c r="I4" t="n">
-        <v>33590852046.15</v>
+        <v>30033337008.79</v>
       </c>
       <c r="J4" t="n">
-        <v>2074818153.87</v>
+        <v>1988167246.33</v>
       </c>
       <c r="K4" t="n">
-        <v>1688752165.85</v>
+        <v>1542959377.24</v>
       </c>
       <c r="L4" t="n">
-        <v>-476517412.05</v>
+        <v>-492590215.89</v>
       </c>
       <c r="M4" t="n">
-        <v>541198550.7</v>
+        <v>596924173.01</v>
       </c>
       <c r="N4" t="n">
-        <v>72869315.59</v>
+        <v>111515808.53</v>
       </c>
       <c r="O4" t="n">
-        <v>921626768.50318</v>
+        <v>720501722.584269</v>
       </c>
       <c r="P4" t="n">
-        <v>745156340.26</v>
+        <v>590940784.1900001</v>
       </c>
       <c r="Q4" t="n">
-        <v>35533432224.66</v>
+        <v>32224000337.64</v>
       </c>
       <c r="R4" t="n">
-        <v>32052783.04</v>
+        <v>27095543.93</v>
       </c>
       <c r="S4" t="n">
-        <v>1160728425.22</v>
+        <v>973528606.37</v>
       </c>
       <c r="T4" t="n">
-        <v>2865985924</v>
+        <v>2814003734</v>
       </c>
       <c r="U4" t="n">
-        <v>2865985924</v>
+        <v>2814003734</v>
       </c>
       <c r="V4" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="W4" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="X4" t="n">
-        <v>745156340.26</v>
+        <v>590940784.1900001</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>745156340.26</v>
+        <v>590940784.1900001</v>
       </c>
       <c r="AA4" t="n">
-        <v>-69589520.86</v>
+        <v>-105533331.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>814745861.12</v>
+        <v>696474115.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>814745861.12</v>
+        <v>696474115.63</v>
       </c>
       <c r="AD4" t="n">
-        <v>332807754.03</v>
+        <v>249561088.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>1147553615.15</v>
+        <v>946035204.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13120300.9</v>
+        <v>-27493402.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>-208465887.51</v>
+        <v>-202182179.71</v>
       </c>
       <c r="AH4" t="n">
-        <v>3337225.55</v>
+        <v>-46738031.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>183471119.7</v>
+        <v>173776795.55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21657542.26</v>
+        <v>75143415.66</v>
       </c>
       <c r="AK4" t="n">
-        <v>-476517412.05</v>
+        <v>-492590215.89</v>
       </c>
       <c r="AL4" t="n">
-        <v>8188176.94</v>
+        <v>7181851.41</v>
       </c>
       <c r="AM4" t="n">
-        <v>541198550.7</v>
+        <v>596924173.01</v>
       </c>
       <c r="AN4" t="n">
-        <v>72869315.59</v>
+        <v>111515808.53</v>
       </c>
       <c r="AO4" t="n">
-        <v>1464285484.1</v>
+        <v>1413318376.79</v>
       </c>
       <c r="AP4" t="n">
-        <v>1942580178.51</v>
+        <v>2190663328.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>373589379.67</v>
+        <v>407129950.94</v>
       </c>
       <c r="AR4" t="n">
-        <v>116317120.91</v>
+        <v>124265926.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>116317120.91</v>
+        <v>124265926.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>380695635.11</v>
+        <v>401450405.76</v>
       </c>
       <c r="AU4" t="n">
-        <v>441765514.62</v>
+        <v>456812799.19</v>
       </c>
       <c r="AV4" t="n">
-        <v>198749393.02</v>
+        <v>221282000.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>243016121.6</v>
+        <v>235530798.44</v>
       </c>
       <c r="AX4" t="n">
-        <v>32052783.04</v>
+        <v>27095543.93</v>
       </c>
       <c r="AY4" t="n">
-        <v>3406865662.61</v>
+        <v>3603981705.64</v>
       </c>
       <c r="AZ4" t="n">
-        <v>33590852046.15</v>
+        <v>30033337008.79</v>
       </c>
       <c r="BA4" t="n">
-        <v>36997717708.76</v>
+        <v>33637318714.43</v>
       </c>
       <c r="BB4" t="n">
-        <v>36997717708.76</v>
+        <v>33637318714.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-7519636.146293</v>
+        <v>-142561052.3125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.218592</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>3909379913.89</v>
+        <v>2037655854.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-34400372.68</v>
+        <v>-570244209.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-34400372.68</v>
+        <v>-570244209.25</v>
       </c>
       <c r="G5" t="n">
-        <v>2249436914.27</v>
+        <v>151656618.41</v>
       </c>
       <c r="H5" t="n">
-        <v>429820434.44</v>
+        <v>425035710.14</v>
       </c>
       <c r="I5" t="n">
-        <v>31897889901.82</v>
+        <v>23121299454.14</v>
       </c>
       <c r="J5" t="n">
-        <v>3874979541.21</v>
+        <v>1467411645.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3445159106.77</v>
+        <v>1042375934.91</v>
       </c>
       <c r="L5" t="n">
-        <v>-461534085.77</v>
+        <v>-459255239.66</v>
       </c>
       <c r="M5" t="n">
-        <v>524516148.83</v>
+        <v>554855426.47</v>
       </c>
       <c r="N5" t="n">
-        <v>82925996.81999999</v>
+        <v>103137736.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2276317650.803707</v>
+        <v>579339775.3475</v>
       </c>
       <c r="P5" t="n">
-        <v>2249436914.27</v>
+        <v>151656618.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>32355817866.23</v>
+        <v>25381547485.98</v>
       </c>
       <c r="R5" t="n">
-        <v>35629987.35</v>
+        <v>29246208.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2929282726.75</v>
+        <v>655231558.11</v>
       </c>
       <c r="T5" t="n">
-        <v>3168221006</v>
+        <v>2765466719</v>
       </c>
       <c r="U5" t="n">
-        <v>3124217936</v>
+        <v>2765466719</v>
       </c>
       <c r="V5" t="n">
-        <v>0.71</v>
+        <v>0.0558</v>
       </c>
       <c r="W5" t="n">
-        <v>0.72</v>
+        <v>0.0558</v>
       </c>
       <c r="X5" t="n">
-        <v>2249436914.27</v>
+        <v>151656618.41</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2249436914.27</v>
+        <v>151656618.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>-32777717.29</v>
+        <v>-133808515.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2282214631.56</v>
+        <v>285465134.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2282214631.56</v>
+        <v>285465134.11</v>
       </c>
       <c r="AD5" t="n">
-        <v>638428326.38</v>
+        <v>202055374.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>2920642957.94</v>
+        <v>487520508.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>-8639768.810000001</v>
+        <v>-167711049.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>-111679124.03</v>
+        <v>-463228533.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>14316173.74</v>
+        <v>103059331.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>71216245.94</v>
+        <v>243044068.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26146704.35</v>
+        <v>117125133.62</v>
       </c>
       <c r="AK5" t="n">
-        <v>-461534085.77</v>
+        <v>-459255239.66</v>
       </c>
       <c r="AL5" t="n">
-        <v>19943933.76</v>
+        <v>7537549.33</v>
       </c>
       <c r="AM5" t="n">
-        <v>524516148.83</v>
+        <v>554855426.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>82925996.81999999</v>
+        <v>103137736.14</v>
       </c>
       <c r="AO5" t="n">
-        <v>3155939994.54</v>
+        <v>1335809885.06</v>
       </c>
       <c r="AP5" t="n">
-        <v>457927964.41</v>
+        <v>2260248031.84</v>
       </c>
       <c r="AQ5" t="n">
-        <v>341604497.39</v>
+        <v>346534437.18</v>
       </c>
       <c r="AR5" t="n">
-        <v>121416720.58</v>
+        <v>140551194.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>121416720.58</v>
+        <v>140551194.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>429427927.47</v>
+        <v>452867236.91</v>
       </c>
       <c r="AU5" t="n">
-        <v>530849031.1</v>
+        <v>488553568.22</v>
       </c>
       <c r="AV5" t="n">
-        <v>187942451.41</v>
+        <v>220535677.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>342906579.69</v>
+        <v>268017890.72</v>
       </c>
       <c r="AX5" t="n">
-        <v>35629987.35</v>
+        <v>29246208.44</v>
       </c>
       <c r="AY5" t="n">
-        <v>3613867958.95</v>
+        <v>3596057916.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31897889901.82</v>
+        <v>23121299454.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>35511757860.77</v>
+        <v>26717357371.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>35511757860.77</v>
+        <v>26717357371.04</v>
       </c>
     </row>
   </sheetData>
@@ -1739,316 +1739,450 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3071456723</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3071456723</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6275606719.87</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14726675411.76</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15428569606.41</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28944537345.62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1637779851.38</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15428569606.41</v>
+      </c>
+      <c r="J2" t="n">
+        <v>137689722.99</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16883461751.27</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22769824350.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17964061351.86</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1080599600.59</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16883461751.27</v>
+      </c>
+      <c r="P2" t="n">
+        <v>261093419.47</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6912108502.19</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6372628459.59</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3071456723</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3071456723</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22926272939.31</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7902245508.79</v>
+      </c>
+      <c r="W2" t="n">
+        <v>324368.99</v>
+      </c>
+      <c r="X2" t="n">
+        <v>507122797.58</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>897771929.73</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>472974090.67</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6024052321.82</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>137689722.99</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5886362598.83</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15024027430.52</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>351405638.42</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8702623089.940001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6174712995.52</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5077522489.82</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1909705917.78</v>
+      </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="n">
-        <v>-330331795.35</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1995750460.43</v>
-      </c>
-      <c r="BT2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>818877024.1799999</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2348939547.86</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>40890334291.17</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24228527009.27</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>970780131.0599999</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>163540492.76</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>374314875.1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1654460986.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1654460986.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>685148865.28</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>15910139005.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1454892144.86</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1124806642.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>330085502.26</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2748267532.58</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1097953197.93</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3846220730.51</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1089226076.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1511266239.93</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>91740590.13</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1153987824.44</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>16661807281.9</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1668880119.56</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>37713728.54</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>761145596.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2664243372.03</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1720667147.39</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>560999616.11</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>56719738.87</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>325856869.66</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4374886166.99</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1369469424.29</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>5785468874.48</v>
+      </c>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
+      <c r="BV2" t="n">
+        <v>5785468874.48</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>685668231.13</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>5099800643.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2787970508</v>
+        <v>2802649508</v>
       </c>
       <c r="C3" t="n">
-        <v>2787970508</v>
+        <v>2802649508</v>
       </c>
       <c r="D3" t="n">
-        <v>5245104363.94</v>
+        <v>6735112619.42</v>
       </c>
       <c r="E3" t="n">
-        <v>16705144298.11</v>
+        <v>15674018746.81</v>
       </c>
       <c r="F3" t="n">
-        <v>15432100111</v>
+        <v>16036077996.21</v>
       </c>
       <c r="G3" t="n">
-        <v>29027124606.76</v>
+        <v>30316992842.15</v>
       </c>
       <c r="H3" t="n">
-        <v>516744476.75</v>
+        <v>2729023359.98</v>
       </c>
       <c r="I3" t="n">
-        <v>15432100111</v>
+        <v>16036077996.21</v>
       </c>
       <c r="J3" t="n">
-        <v>235963378.01</v>
+        <v>130407554.13</v>
       </c>
       <c r="K3" t="n">
-        <v>17252567092.27</v>
+        <v>17394203366.99</v>
       </c>
       <c r="L3" t="n">
-        <v>23655951266.5</v>
+        <v>24900175861.83</v>
       </c>
       <c r="M3" t="n">
-        <v>18835594423.61</v>
+        <v>18460992062.22</v>
       </c>
       <c r="N3" t="n">
-        <v>1583027331.34</v>
+        <v>1066788695.23</v>
       </c>
       <c r="O3" t="n">
-        <v>17252567092.27</v>
+        <v>17394203366.99</v>
       </c>
       <c r="P3" t="n">
-        <v>200041622.28</v>
+        <v>230720732.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>7458818292.06</v>
+        <v>7351061025.26</v>
       </c>
       <c r="R3" t="n">
-        <v>6494160207.39</v>
+        <v>6789468791.97</v>
       </c>
       <c r="S3" t="n">
-        <v>2787970508</v>
+        <v>2802649508</v>
       </c>
       <c r="T3" t="n">
-        <v>2787970508</v>
+        <v>2802649508</v>
       </c>
       <c r="U3" t="n">
-        <v>22994764813.43</v>
+        <v>22773539860.34</v>
       </c>
       <c r="V3" t="n">
-        <v>8514881810</v>
+        <v>9608729687.15</v>
       </c>
       <c r="W3" t="n">
-        <v>105473304.2</v>
+        <v>175642.96</v>
       </c>
       <c r="X3" t="n">
-        <v>355759535.94</v>
+        <v>501848527.54</v>
       </c>
       <c r="Y3" t="n">
-        <v>854670186.26</v>
+        <v>896128258.1900001</v>
       </c>
       <c r="Z3" t="n">
-        <v>559631231.36</v>
+        <v>574197209.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>6639347552.24</v>
+        <v>7636380048.97</v>
       </c>
       <c r="AB3" t="n">
-        <v>235963378.01</v>
+        <v>130407554.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>6403384174.23</v>
+        <v>7505972494.84</v>
       </c>
       <c r="AD3" t="n">
-        <v>14479883003.43</v>
+        <v>13164810173.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>274820905.2</v>
+        <v>320191600.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>10065796745.87</v>
+        <v>8037638697.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>5371173340.26</v>
+        <v>5416816980.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>3704987066.98</v>
+        <v>4099800076.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>1159840475.44</v>
+        <v>1588782984.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500000</v>
+        <v>2450000</v>
       </c>
       <c r="AK3" t="n">
-        <v>375158340.76</v>
+        <v>442821144.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>2169488250.78</v>
+        <v>2065745947.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>41830359237.04</v>
+        <v>41234531922.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>26833731756.86</v>
+        <v>25340698389.39</v>
       </c>
       <c r="AO3" t="n">
-        <v>640293318.2</v>
+        <v>1076604768.99</v>
       </c>
       <c r="AP3" t="n">
-        <v>93163236.14</v>
+        <v>153305830.46</v>
       </c>
       <c r="AQ3" t="n">
-        <v>279792425.97</v>
+        <v>350585821.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>1091832133.09</v>
+        <v>1388295447.94</v>
       </c>
       <c r="AS3" t="n">
-        <v>1091832133.09</v>
+        <v>1388295447.94</v>
       </c>
       <c r="AT3" t="n">
-        <v>2056876443.76</v>
+        <v>726139898.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>18068367378.01</v>
+        <v>17185444142.86</v>
       </c>
       <c r="AV3" t="n">
-        <v>1820466981.27</v>
+        <v>1358125370.78</v>
       </c>
       <c r="AW3" t="n">
-        <v>1513156014.41</v>
+        <v>1045045365.29</v>
       </c>
       <c r="AX3" t="n">
-        <v>307310966.86</v>
+        <v>313080005.49</v>
       </c>
       <c r="AY3" t="n">
-        <v>2750155032.2</v>
+        <v>2917548200.43</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1571175895.52</v>
+        <v>-1232567652.83</v>
       </c>
       <c r="BA3" t="n">
-        <v>4321330927.72</v>
+        <v>4150115853.26</v>
       </c>
       <c r="BB3" t="n">
-        <v>348136229.01</v>
+        <v>961272572.0599999</v>
       </c>
       <c r="BC3" t="n">
-        <v>2165085421.55</v>
+        <v>1766531916.93</v>
       </c>
       <c r="BD3" t="n">
-        <v>49916774.6</v>
+        <v>66846131.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>1758192502.56</v>
+        <v>1355465233.12</v>
       </c>
       <c r="BF3" t="n">
-        <v>14996627480.18</v>
+        <v>15893833533.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>970221302.73</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>16160000</v>
-      </c>
+        <v>1147520636.56</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>325719332.58</v>
+        <v>595925792.9400001</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1757974142.22</v>
+        <v>2240058505.31</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>834866069.63</v>
+        <v>1325914055.32</v>
       </c>
       <c r="BM3" t="n">
-        <v>524794016.62</v>
+        <v>533578490.19</v>
       </c>
       <c r="BN3" t="n">
-        <v>57913511.77</v>
+        <v>54523875.05</v>
       </c>
       <c r="BO3" t="n">
-        <v>340400544.2</v>
+        <v>326042084.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>3768537384.35</v>
+        <v>4415091811.77</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1614189167.75</v>
+        <v>1307559930.85</v>
       </c>
       <c r="BR3" t="n">
-        <v>-338240016.98</v>
+        <v>-364601274.32</v>
       </c>
       <c r="BS3" t="n">
-        <v>1952429184.73</v>
+        <v>1672161205.17</v>
       </c>
       <c r="BT3" t="n">
-        <v>6543826150.55</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>14373000</v>
-      </c>
+        <v>6187676855.74</v>
+      </c>
+      <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>6529453150.55</v>
+        <v>6187676855.74</v>
       </c>
       <c r="BW3" t="n">
-        <v>1700348311.65</v>
+        <v>705210701.34</v>
       </c>
       <c r="BX3" t="n">
-        <v>4683629841.42</v>
+        <v>5466007212.96</v>
       </c>
     </row>
     <row r="4">
@@ -2283,451 +2417,317 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2802649508</v>
+        <v>2787970508</v>
       </c>
       <c r="C5" t="n">
-        <v>2802649508</v>
+        <v>2787970508</v>
       </c>
       <c r="D5" t="n">
-        <v>6735112619.42</v>
+        <v>5245104363.94</v>
       </c>
       <c r="E5" t="n">
-        <v>15674018746.81</v>
+        <v>16705144298.11</v>
       </c>
       <c r="F5" t="n">
-        <v>16036077996.21</v>
+        <v>15432100111</v>
       </c>
       <c r="G5" t="n">
-        <v>30316992842.15</v>
+        <v>29027124606.76</v>
       </c>
       <c r="H5" t="n">
-        <v>2729023359.98</v>
+        <v>516744476.75</v>
       </c>
       <c r="I5" t="n">
-        <v>16036077996.21</v>
+        <v>15432100111</v>
       </c>
       <c r="J5" t="n">
-        <v>130407554.13</v>
+        <v>235963378.01</v>
       </c>
       <c r="K5" t="n">
-        <v>17394203366.99</v>
+        <v>17252567092.27</v>
       </c>
       <c r="L5" t="n">
-        <v>24900175861.83</v>
+        <v>23655951266.5</v>
       </c>
       <c r="M5" t="n">
-        <v>18460992062.22</v>
+        <v>18835594423.61</v>
       </c>
       <c r="N5" t="n">
-        <v>1066788695.23</v>
+        <v>1583027331.34</v>
       </c>
       <c r="O5" t="n">
-        <v>17394203366.99</v>
+        <v>17252567092.27</v>
       </c>
       <c r="P5" t="n">
-        <v>230720732.28</v>
+        <v>200041622.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>7351061025.26</v>
+        <v>7458818292.06</v>
       </c>
       <c r="R5" t="n">
-        <v>6789468791.97</v>
+        <v>6494160207.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2802649508</v>
+        <v>2787970508</v>
       </c>
       <c r="T5" t="n">
-        <v>2802649508</v>
+        <v>2787970508</v>
       </c>
       <c r="U5" t="n">
-        <v>22773539860.34</v>
+        <v>22994764813.43</v>
       </c>
       <c r="V5" t="n">
-        <v>9608729687.15</v>
+        <v>8514881810</v>
       </c>
       <c r="W5" t="n">
-        <v>175642.96</v>
+        <v>105473304.2</v>
       </c>
       <c r="X5" t="n">
-        <v>501848527.54</v>
+        <v>355759535.94</v>
       </c>
       <c r="Y5" t="n">
-        <v>896128258.1900001</v>
+        <v>854670186.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>574197209.49</v>
+        <v>559631231.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>7636380048.97</v>
+        <v>6639347552.24</v>
       </c>
       <c r="AB5" t="n">
-        <v>130407554.13</v>
+        <v>235963378.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>7505972494.84</v>
+        <v>6403384174.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>13164810173.19</v>
+        <v>14479883003.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>320191600.15</v>
+        <v>274820905.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>8037638697.84</v>
+        <v>10065796745.87</v>
       </c>
       <c r="AG5" t="n">
-        <v>5416816980.32</v>
+        <v>5371173340.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>4099800076.17</v>
+        <v>3704987066.98</v>
       </c>
       <c r="AI5" t="n">
-        <v>1588782984.57</v>
+        <v>1159840475.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2450000</v>
+        <v>500000</v>
       </c>
       <c r="AK5" t="n">
-        <v>442821144.1</v>
+        <v>375158340.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>2065745947.5</v>
+        <v>2169488250.78</v>
       </c>
       <c r="AM5" t="n">
-        <v>41234531922.56</v>
+        <v>41830359237.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>25340698389.39</v>
+        <v>26833731756.86</v>
       </c>
       <c r="AO5" t="n">
-        <v>1076604768.99</v>
+        <v>640293318.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>153305830.46</v>
+        <v>93163236.14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>350585821.09</v>
+        <v>279792425.97</v>
       </c>
       <c r="AR5" t="n">
-        <v>1388295447.94</v>
+        <v>1091832133.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>1388295447.94</v>
+        <v>1091832133.09</v>
       </c>
       <c r="AT5" t="n">
-        <v>726139898.03</v>
+        <v>2056876443.76</v>
       </c>
       <c r="AU5" t="n">
-        <v>17185444142.86</v>
+        <v>18068367378.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1358125370.78</v>
+        <v>1820466981.27</v>
       </c>
       <c r="AW5" t="n">
-        <v>1045045365.29</v>
+        <v>1513156014.41</v>
       </c>
       <c r="AX5" t="n">
-        <v>313080005.49</v>
+        <v>307310966.86</v>
       </c>
       <c r="AY5" t="n">
-        <v>2917548200.43</v>
+        <v>2750155032.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1232567652.83</v>
+        <v>-1571175895.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>4150115853.26</v>
+        <v>4321330927.72</v>
       </c>
       <c r="BB5" t="n">
-        <v>961272572.0599999</v>
+        <v>348136229.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1766531916.93</v>
+        <v>2165085421.55</v>
       </c>
       <c r="BD5" t="n">
-        <v>66846131.15</v>
+        <v>49916774.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1355465233.12</v>
+        <v>1758192502.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>15893833533.17</v>
+        <v>14996627480.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>1147520636.56</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
+        <v>970221302.73</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>16160000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>595925792.9400001</v>
+        <v>325719332.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2240058505.31</v>
+        <v>1757974142.22</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1325914055.32</v>
+        <v>834866069.63</v>
       </c>
       <c r="BM5" t="n">
-        <v>533578490.19</v>
+        <v>524794016.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>54523875.05</v>
+        <v>57913511.77</v>
       </c>
       <c r="BO5" t="n">
-        <v>326042084.75</v>
+        <v>340400544.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>4415091811.77</v>
+        <v>3768537384.35</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1307559930.85</v>
+        <v>1614189167.75</v>
       </c>
       <c r="BR5" t="n">
-        <v>-364601274.32</v>
+        <v>-338240016.98</v>
       </c>
       <c r="BS5" t="n">
-        <v>1672161205.17</v>
+        <v>1952429184.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>6187676855.74</v>
-      </c>
-      <c r="BU5" t="inlineStr"/>
+        <v>6543826150.55</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>14373000</v>
+      </c>
       <c r="BV5" t="n">
-        <v>6187676855.74</v>
+        <v>6529453150.55</v>
       </c>
       <c r="BW5" t="n">
-        <v>705210701.34</v>
+        <v>1700348311.65</v>
       </c>
       <c r="BX5" t="n">
-        <v>5466007212.96</v>
+        <v>4683629841.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3071456723</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3071456723</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6275606719.87</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14726675411.76</v>
-      </c>
-      <c r="F6" t="n">
-        <v>15428569606.41</v>
-      </c>
-      <c r="G6" t="n">
-        <v>28944537345.62</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1637779851.38</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15428569606.41</v>
-      </c>
-      <c r="J6" t="n">
-        <v>137689722.99</v>
-      </c>
-      <c r="K6" t="n">
-        <v>16883461751.27</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22769824350.1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17964061351.86</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1080599600.59</v>
-      </c>
-      <c r="O6" t="n">
-        <v>16883461751.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>261093419.47</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6912108502.19</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6372628459.59</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3071456723</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3071456723</v>
-      </c>
-      <c r="U6" t="n">
-        <v>22926272939.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>7902245508.79</v>
-      </c>
-      <c r="W6" t="n">
-        <v>324368.99</v>
-      </c>
-      <c r="X6" t="n">
-        <v>507122797.58</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>897771929.73</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>472974090.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6024052321.82</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>137689722.99</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5886362598.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15024027430.52</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>351405638.42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8702623089.940001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>6174712995.52</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>5077522489.82</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1909705917.78</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="n">
-        <v>818877024.1799999</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2348939547.86</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>40890334291.17</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>24228527009.27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>970780131.0599999</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>163540492.76</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>374314875.1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1654460986.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1654460986.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>685148865.28</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>15910139005.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1454892144.86</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1124806642.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>330085502.26</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2748267532.58</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-1097953197.93</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3846220730.51</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1089226076.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1511266239.93</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>91740590.13</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1153987824.44</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>16661807281.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1668880119.56</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>37713728.54</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>761145596.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>2664243372.03</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1720667147.39</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>560999616.11</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>56719738.87</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>325856869.66</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>4374886166.99</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1369469424.29</v>
-      </c>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="n">
-        <v>5785468874.48</v>
-      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>-330331795.35</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1995750460.43</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="n">
-        <v>5785468874.48</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>685668231.13</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>5099800643.35</v>
-      </c>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2992,604 +2992,604 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>596092127.33</v>
+        <v>-1825504549.16</v>
       </c>
       <c r="C2" t="n">
-        <v>-8894366098.17</v>
+        <v>-7771241179.6</v>
       </c>
       <c r="D2" t="n">
-        <v>9568080127.6</v>
+        <v>8947287307.360001</v>
       </c>
       <c r="E2" t="n">
-        <v>-1064702775.89</v>
+        <v>-3152150220.28</v>
       </c>
       <c r="F2" t="n">
-        <v>6386432189.26</v>
+        <v>5062294132.9</v>
       </c>
       <c r="G2" t="n">
-        <v>4843020692.55</v>
+        <v>4688995314.95</v>
       </c>
       <c r="H2" t="n">
-        <v>3943850.19</v>
+        <v>-7244997.71</v>
       </c>
       <c r="I2" t="n">
-        <v>1539467646.52</v>
+        <v>380543815.66</v>
       </c>
       <c r="J2" t="n">
-        <v>-215935271.89</v>
+        <v>1166624780.81</v>
       </c>
       <c r="K2" t="n">
-        <v>-112016993.7</v>
+        <v>1009867918.07</v>
       </c>
       <c r="L2" t="n">
-        <v>-747955030.91</v>
+        <v>-931422559.9299999</v>
       </c>
       <c r="M2" t="n">
-        <v>673714029.4299999</v>
+        <v>1176046127.76</v>
       </c>
       <c r="N2" t="n">
-        <v>673714029.4299999</v>
+        <v>1176046127.76</v>
       </c>
       <c r="O2" t="n">
-        <v>-8894366098.17</v>
+        <v>-7771241179.6</v>
       </c>
       <c r="P2" t="n">
-        <v>9568080127.6</v>
+        <v>8947287307.360001</v>
       </c>
       <c r="Q2" t="n">
-        <v>94608015.19</v>
+        <v>-2112726636.27</v>
       </c>
       <c r="R2" t="n">
-        <v>119197236.66</v>
+        <v>-20251330.06</v>
       </c>
       <c r="S2" t="n">
-        <v>204042947.21</v>
+        <v>170614616.81</v>
       </c>
       <c r="T2" t="n">
-        <v>294053847.21</v>
+        <v>237118451.52</v>
       </c>
       <c r="U2" t="n">
-        <v>-90010900</v>
+        <v>-66503834.71</v>
       </c>
       <c r="V2" t="n">
-        <v>577154250.58</v>
+        <v>836173282.3200001</v>
       </c>
       <c r="W2" t="n">
-        <v>577154250.58</v>
+        <v>836173282.3200001</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-805786419.26</v>
+        <v>-3099263205.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>258916356.63</v>
+        <v>52887014.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1064702775.89</v>
+        <v>-3152150220.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>1660794903.22</v>
+        <v>1326645671.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>82842956.81</v>
+        <v>-1896051167.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>23861468.83</v>
+        <v>74953200.06999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>117979222.88</v>
+        <v>1237625620.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>-72228865.11</v>
+        <v>-1342544753.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>13231130.21</v>
+        <v>-1866085233.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>556812243.21</v>
+        <v>657206760.63</v>
       </c>
       <c r="AI2" t="n">
-        <v>425035710.14</v>
+        <v>429820434.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>330220336.2</v>
+        <v>342817606.76</v>
       </c>
       <c r="AK2" t="n">
-        <v>-203233666.95</v>
+        <v>-359980787.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>125868754</v>
+        <v>14992993.54</v>
       </c>
       <c r="AM2" t="n">
-        <v>285465134.11</v>
+        <v>2282214631.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>1660794903.22</v>
+        <v>1326645671.12</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1946663280.49</v>
+        <v>-2281598826.45</v>
       </c>
       <c r="AP2" t="n">
-        <v>51712931.76</v>
+        <v>134708386.46</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-9354357.189999999</v>
+        <v>-16717018.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>-23847909051.38</v>
+        <v>-36983143022.97</v>
       </c>
       <c r="AS2" t="n">
-        <v>-889061673.33</v>
+        <v>-1729398026.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1562545109.53</v>
+        <v>-1422400179.83</v>
       </c>
       <c r="AU2" t="n">
-        <v>-21396302268.52</v>
+        <v>-33831344816.52</v>
       </c>
       <c r="AV2" t="n">
-        <v>27413008660.52</v>
+        <v>40473396152.72</v>
       </c>
       <c r="AW2" t="n">
-        <v>735907995.62</v>
+        <v>3105113363.09</v>
       </c>
       <c r="AX2" t="n">
-        <v>26677100664.9</v>
+        <v>37368282789.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>316645084.3</v>
+        <v>-365983137.25</v>
       </c>
       <c r="C3" t="n">
-        <v>-9199141546.82</v>
+        <v>-9970608128.190001</v>
       </c>
       <c r="D3" t="n">
-        <v>9591814045.629999</v>
+        <v>11201872557.87</v>
       </c>
       <c r="E3" t="n">
-        <v>-1394059247.7</v>
+        <v>-1853859770.01</v>
       </c>
       <c r="F3" t="n">
-        <v>4843020692.55</v>
+        <v>5467168088.71</v>
       </c>
       <c r="G3" t="n">
-        <v>5467168088.71</v>
+        <v>5062294132.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-28320094.24</v>
+        <v>21746657.07</v>
       </c>
       <c r="I3" t="n">
-        <v>-595827301.92</v>
+        <v>383127298.74</v>
       </c>
       <c r="J3" t="n">
-        <v>-405185486.86</v>
+        <v>230219135.28</v>
       </c>
       <c r="K3" t="n">
-        <v>68472459.43000001</v>
+        <v>-178317443.61</v>
       </c>
       <c r="L3" t="n">
-        <v>-828693541.71</v>
+        <v>-782098437.4299999</v>
       </c>
       <c r="M3" t="n">
-        <v>392672498.81</v>
+        <v>1231264429.68</v>
       </c>
       <c r="N3" t="n">
-        <v>392672498.81</v>
+        <v>1231264429.68</v>
       </c>
       <c r="O3" t="n">
-        <v>-9199141546.82</v>
+        <v>-9970608128.190001</v>
       </c>
       <c r="P3" t="n">
-        <v>9591814045.629999</v>
+        <v>11201872557.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1901346147.06</v>
+        <v>-1334968469.3</v>
       </c>
       <c r="R3" t="n">
-        <v>83441558.73</v>
+        <v>48496679.86</v>
       </c>
       <c r="S3" t="n">
-        <v>-1085802594.85</v>
+        <v>-31817252.79</v>
       </c>
       <c r="T3" t="n">
-        <v>191497405.15</v>
+        <v>160054930.67</v>
       </c>
       <c r="U3" t="n">
-        <v>-1277300000</v>
+        <v>-191872183.46</v>
       </c>
       <c r="V3" t="n">
-        <v>366458133.61</v>
+        <v>380368590.01</v>
       </c>
       <c r="W3" t="n">
-        <v>388695807.56</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-22237673.95</v>
-      </c>
+        <v>380368590.01</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-1265443244.55</v>
+        <v>-1732016486.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>128616003.15</v>
+        <v>121843283.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1394059247.7</v>
+        <v>-1853859770.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1710704332</v>
+        <v>1487876632.76</v>
       </c>
       <c r="AC3" t="n">
-        <v>-84568688.98999999</v>
+        <v>-195264823.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>23535914.18</v>
+        <v>160550586.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>-649640162.0700001</v>
+        <v>-94595829.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>45095929.67</v>
+        <v>-129054788.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>496439629.23</v>
+        <v>-132164792.48</v>
       </c>
       <c r="AH3" t="n">
-        <v>749065875.4</v>
+        <v>622671513.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>445207869.09</v>
+        <v>386065988.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>365234272.83</v>
+        <v>311693527.55</v>
       </c>
       <c r="AK3" t="n">
-        <v>-314467068.31</v>
+        <v>-356779395.93</v>
       </c>
       <c r="AL3" t="n">
-        <v>-43168106.58</v>
+        <v>7697928.74</v>
       </c>
       <c r="AM3" t="n">
-        <v>696474115.63</v>
+        <v>814745861.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>1710704332</v>
+        <v>1487876632.76</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2488169811.18</v>
+        <v>-2664375835.66</v>
       </c>
       <c r="AP3" t="n">
-        <v>61705188.01</v>
+        <v>104468916.11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-762340.88</v>
+        <v>-6515905.59</v>
       </c>
       <c r="AR3" t="n">
-        <v>-33540654155.52</v>
+        <v>-36494738245.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>-854183196.99</v>
+        <v>-1395035069.27</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1543516318.2</v>
+        <v>-1554086851.89</v>
       </c>
       <c r="AU3" t="n">
-        <v>-31142954640.33</v>
+        <v>-33545616324.13</v>
       </c>
       <c r="AV3" t="n">
-        <v>37678585451.57</v>
+        <v>40549037703.19</v>
       </c>
       <c r="AW3" t="n">
-        <v>761070135.36</v>
+        <v>2068443722.93</v>
       </c>
       <c r="AX3" t="n">
-        <v>36917515316.21</v>
+        <v>38480593980.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-365983137.25</v>
+        <v>316645084.3</v>
       </c>
       <c r="C4" t="n">
-        <v>-9970608128.190001</v>
+        <v>-9199141546.82</v>
       </c>
       <c r="D4" t="n">
-        <v>11201872557.87</v>
+        <v>9591814045.629999</v>
       </c>
       <c r="E4" t="n">
-        <v>-1853859770.01</v>
+        <v>-1394059247.7</v>
       </c>
       <c r="F4" t="n">
+        <v>4843020692.55</v>
+      </c>
+      <c r="G4" t="n">
         <v>5467168088.71</v>
       </c>
-      <c r="G4" t="n">
-        <v>5062294132.9</v>
-      </c>
       <c r="H4" t="n">
-        <v>21746657.07</v>
+        <v>-28320094.24</v>
       </c>
       <c r="I4" t="n">
-        <v>383127298.74</v>
+        <v>-595827301.92</v>
       </c>
       <c r="J4" t="n">
-        <v>230219135.28</v>
+        <v>-405185486.86</v>
       </c>
       <c r="K4" t="n">
-        <v>-178317443.61</v>
+        <v>68472459.43000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-782098437.4299999</v>
+        <v>-828693541.71</v>
       </c>
       <c r="M4" t="n">
-        <v>1231264429.68</v>
+        <v>392672498.81</v>
       </c>
       <c r="N4" t="n">
-        <v>1231264429.68</v>
+        <v>392672498.81</v>
       </c>
       <c r="O4" t="n">
-        <v>-9970608128.190001</v>
+        <v>-9199141546.82</v>
       </c>
       <c r="P4" t="n">
-        <v>11201872557.87</v>
+        <v>9591814045.629999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1334968469.3</v>
+        <v>-1901346147.06</v>
       </c>
       <c r="R4" t="n">
-        <v>48496679.86</v>
+        <v>83441558.73</v>
       </c>
       <c r="S4" t="n">
-        <v>-31817252.79</v>
+        <v>-1085802594.85</v>
       </c>
       <c r="T4" t="n">
-        <v>160054930.67</v>
+        <v>191497405.15</v>
       </c>
       <c r="U4" t="n">
-        <v>-191872183.46</v>
+        <v>-1277300000</v>
       </c>
       <c r="V4" t="n">
-        <v>380368590.01</v>
+        <v>366458133.61</v>
       </c>
       <c r="W4" t="n">
-        <v>380368590.01</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>388695807.56</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-22237673.95</v>
+      </c>
       <c r="Y4" t="n">
-        <v>-1732016486.38</v>
+        <v>-1265443244.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>121843283.63</v>
+        <v>128616003.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1853859770.01</v>
+        <v>-1394059247.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1487876632.76</v>
+        <v>1710704332</v>
       </c>
       <c r="AC4" t="n">
-        <v>-195264823.66</v>
+        <v>-84568688.98999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>160550586.94</v>
+        <v>23535914.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>-94595829.19</v>
+        <v>-649640162.0700001</v>
       </c>
       <c r="AF4" t="n">
-        <v>-129054788.93</v>
+        <v>45095929.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>-132164792.48</v>
+        <v>496439629.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>622671513.24</v>
+        <v>749065875.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>386065988.02</v>
+        <v>445207869.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>311693527.55</v>
+        <v>365234272.83</v>
       </c>
       <c r="AK4" t="n">
-        <v>-356779395.93</v>
+        <v>-314467068.31</v>
       </c>
       <c r="AL4" t="n">
-        <v>7697928.74</v>
+        <v>-43168106.58</v>
       </c>
       <c r="AM4" t="n">
-        <v>814745861.12</v>
+        <v>696474115.63</v>
       </c>
       <c r="AN4" t="n">
-        <v>1487876632.76</v>
+        <v>1710704332</v>
       </c>
       <c r="AO4" t="n">
-        <v>-2664375835.66</v>
+        <v>-2488169811.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>104468916.11</v>
+        <v>61705188.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-6515905.59</v>
+        <v>-762340.88</v>
       </c>
       <c r="AR4" t="n">
-        <v>-36494738245.29</v>
+        <v>-33540654155.52</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1395035069.27</v>
+        <v>-854183196.99</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1554086851.89</v>
+        <v>-1543516318.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>-33545616324.13</v>
+        <v>-31142954640.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>40549037703.19</v>
+        <v>37678585451.57</v>
       </c>
       <c r="AW4" t="n">
-        <v>2068443722.93</v>
+        <v>761070135.36</v>
       </c>
       <c r="AX4" t="n">
-        <v>38480593980.26</v>
+        <v>36917515316.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1825504549.16</v>
+        <v>596092127.33</v>
       </c>
       <c r="C5" t="n">
-        <v>-7771241179.6</v>
+        <v>-8894366098.17</v>
       </c>
       <c r="D5" t="n">
-        <v>8947287307.360001</v>
+        <v>9568080127.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-3152150220.28</v>
+        <v>-1064702775.89</v>
       </c>
       <c r="F5" t="n">
-        <v>5062294132.9</v>
+        <v>6386432189.26</v>
       </c>
       <c r="G5" t="n">
-        <v>4688995314.95</v>
+        <v>4843020692.55</v>
       </c>
       <c r="H5" t="n">
-        <v>-7244997.71</v>
+        <v>3943850.19</v>
       </c>
       <c r="I5" t="n">
-        <v>380543815.66</v>
+        <v>1539467646.52</v>
       </c>
       <c r="J5" t="n">
-        <v>1166624780.81</v>
+        <v>-215935271.89</v>
       </c>
       <c r="K5" t="n">
-        <v>1009867918.07</v>
+        <v>-112016993.7</v>
       </c>
       <c r="L5" t="n">
-        <v>-931422559.9299999</v>
+        <v>-747955030.91</v>
       </c>
       <c r="M5" t="n">
-        <v>1176046127.76</v>
+        <v>673714029.4299999</v>
       </c>
       <c r="N5" t="n">
-        <v>1176046127.76</v>
+        <v>673714029.4299999</v>
       </c>
       <c r="O5" t="n">
-        <v>-7771241179.6</v>
+        <v>-8894366098.17</v>
       </c>
       <c r="P5" t="n">
-        <v>8947287307.360001</v>
+        <v>9568080127.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2112726636.27</v>
+        <v>94608015.19</v>
       </c>
       <c r="R5" t="n">
-        <v>-20251330.06</v>
+        <v>119197236.66</v>
       </c>
       <c r="S5" t="n">
-        <v>170614616.81</v>
+        <v>204042947.21</v>
       </c>
       <c r="T5" t="n">
-        <v>237118451.52</v>
+        <v>294053847.21</v>
       </c>
       <c r="U5" t="n">
-        <v>-66503834.71</v>
+        <v>-90010900</v>
       </c>
       <c r="V5" t="n">
-        <v>836173282.3200001</v>
+        <v>577154250.58</v>
       </c>
       <c r="W5" t="n">
-        <v>836173282.3200001</v>
+        <v>577154250.58</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-3099263205.34</v>
+        <v>-805786419.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>52887014.94</v>
+        <v>258916356.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3152150220.28</v>
+        <v>-1064702775.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>1326645671.12</v>
+        <v>1660794903.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1896051167.05</v>
+        <v>82842956.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>74953200.06999999</v>
+        <v>23861468.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>1237625620.15</v>
+        <v>117979222.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1342544753.7</v>
+        <v>-72228865.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1866085233.57</v>
+        <v>13231130.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>657206760.63</v>
+        <v>556812243.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>429820434.44</v>
+        <v>425035710.14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>342817606.76</v>
+        <v>330220336.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>-359980787.1</v>
+        <v>-203233666.95</v>
       </c>
       <c r="AL5" t="n">
-        <v>14992993.54</v>
+        <v>125868754</v>
       </c>
       <c r="AM5" t="n">
-        <v>2282214631.56</v>
+        <v>285465134.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>1326645671.12</v>
+        <v>1660794903.22</v>
       </c>
       <c r="AO5" t="n">
-        <v>-2281598826.45</v>
+        <v>-1946663280.49</v>
       </c>
       <c r="AP5" t="n">
-        <v>134708386.46</v>
+        <v>51712931.76</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-16717018.64</v>
+        <v>-9354357.189999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>-36983143022.97</v>
+        <v>-23847909051.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1729398026.62</v>
+        <v>-889061673.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1422400179.83</v>
+        <v>-1562545109.53</v>
       </c>
       <c r="AU5" t="n">
-        <v>-33831344816.52</v>
+        <v>-21396302268.52</v>
       </c>
       <c r="AV5" t="n">
-        <v>40473396152.72</v>
+        <v>27413008660.52</v>
       </c>
       <c r="AW5" t="n">
-        <v>3105113363.09</v>
+        <v>735907995.62</v>
       </c>
       <c r="AX5" t="n">
-        <v>37368282789.63</v>
+        <v>26677100664.9</v>
       </c>
     </row>
   </sheetData>
@@ -4184,187 +4184,187 @@
       </c>
       <c r="DL1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EW1" t="inlineStr">
@@ -4456,37 +4456,37 @@
         <v>86400</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="T2" t="n">
-        <v>5.34</v>
+        <v>4.86</v>
       </c>
       <c r="U2" t="n">
-        <v>5.31</v>
+        <v>4.72</v>
       </c>
       <c r="V2" t="n">
-        <v>5.46</v>
+        <v>4.89</v>
       </c>
       <c r="W2" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="X2" t="n">
-        <v>5.34</v>
+        <v>4.86</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.31</v>
+        <v>4.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.46</v>
+        <v>4.89</v>
       </c>
       <c r="AA2" t="n">
         <v>0.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.81</v>
+        <v>3.07</v>
       </c>
       <c r="AC2" t="n">
         <v>1761782400</v>
@@ -4498,34 +4498,34 @@
         <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.749</v>
+        <v>0.663</v>
       </c>
       <c r="AG2" t="n">
-        <v>22.208334</v>
+        <v>20.375</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.035713</v>
+        <v>17.464285</v>
       </c>
       <c r="AI2" t="n">
-        <v>27701751</v>
+        <v>26423181</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27701751</v>
+        <v>26423181</v>
       </c>
       <c r="AK2" t="n">
-        <v>25339091</v>
+        <v>23143759</v>
       </c>
       <c r="AL2" t="n">
-        <v>24107220</v>
+        <v>19940592</v>
       </c>
       <c r="AM2" t="n">
-        <v>24107220</v>
+        <v>19940592</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.32</v>
+        <v>4.88</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.33</v>
+        <v>4.89</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>14732284928</v>
+        <v>13516110848</v>
       </c>
       <c r="AS2" t="n">
-        <v>14732284739</v>
+        <v>13516111140</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>4.72</v>
       </c>
       <c r="AU2" t="n">
         <v>7.39</v>
@@ -4552,19 +4552,19 @@
         <v>1.675</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.6399751299999999</v>
+        <v>0.58714414</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.6892</v>
+        <v>5.491</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.1129</v>
+        <v>6.03575</v>
       </c>
       <c r="BA2" t="n">
         <v>0.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.027881041</v>
+        <v>0.030674849</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>26170935296</v>
+        <v>24954761216</v>
       </c>
       <c r="BF2" t="n">
         <v>0.02863</v>
@@ -4599,7 +4599,7 @@
         <v>6.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.81126326</v>
+        <v>0.7442922</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4631,16 +4631,16 @@
         <v>1305763200</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.137</v>
+        <v>1.084</v>
       </c>
       <c r="BX2" t="n">
-        <v>19.851</v>
+        <v>18.929</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.049910903</v>
+        <v>-0.073863626</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.05</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>5.33</v>
+        <v>4.89</v>
       </c>
       <c r="CE2" t="n">
         <v>6.58</v>
@@ -4771,140 +4771,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DL2" t="n">
-        <v>-0.92937154</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="DN2" t="b">
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>TRANSFAR ZHILIAN CO LTD</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Transfar Zhilian Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1782111885</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_303901165</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
         <v>1088472600000</v>
       </c>
-      <c r="DP2" t="n">
-        <v>-0.05000019</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>5.31 - 5.46</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>4.72 - 4.89</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>25339091</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.13000011</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.025000023</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>5.2 - 7.39</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.27875507</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-4.9910903</v>
-      </c>
-      <c r="DZ2" t="n">
+      <c r="EH2" t="n">
+        <v>23143759</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.17000008</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.036016967</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>4.72 - 7.39</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.338295</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-7.3863626</v>
+      </c>
+      <c r="EO2" t="n">
         <v>1651229940</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EP2" t="n">
         <v>1651492800</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EQ2" t="n">
         <v>0.24</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="ER2" t="n">
         <v>0.28</v>
       </c>
-      <c r="ED2" t="n">
-        <v>-0.3592</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.06313717000000001</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.78289986</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.1280734</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>TRANSFAR ZHILIAN CO LTD</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Transfar Zhilian Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EN2" t="n">
-        <v>1780038294</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>finmb_303901165</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
       <c r="ES2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+        <v>-0.6010003</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-0.10945188</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-1.14575</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.1898273</v>
       </c>
       <c r="EW2" t="inlineStr"/>
     </row>
